--- a/data/processed/gyeongnam_high_schools_CDI.xlsx
+++ b/data/processed/gyeongnam_high_schools_CDI.xlsx
@@ -1035,7 +1035,7 @@
         <v>203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G9" t="n">
         <v>157.3333333333333</v>
@@ -1059,10 +1059,10 @@
         <v>0.03243243243243243</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1106,7 +1106,7 @@
         <v>487</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G10" t="n">
         <v>232.6666666666666</v>
@@ -1130,10 +1130,10 @@
         <v>0.02553191489361702</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1177,7 +1177,7 @@
         <v>451</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G11" t="n">
         <v>449</v>
@@ -1201,10 +1201,10 @@
         <v>0.07037764675526569</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1248,7 +1248,7 @@
         <v>319</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G12" t="n">
         <v>468.6666666666667</v>
@@ -1272,10 +1272,10 @@
         <v>0.2339320004518243</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 상위</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         <v>277</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="P13" t="n">
         <v>3</v>
@@ -1390,7 +1390,7 @@
         <v>297</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G14" t="n">
         <v>139</v>
@@ -1414,10 +1414,10 @@
         <v>0.07086614173228346</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
@@ -1461,7 +1461,7 @@
         <v>384</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G15" t="n">
         <v>276.6666666666667</v>
@@ -1485,10 +1485,10 @@
         <v>0.04477611940298508</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="P15" t="n">
         <v>3</v>
@@ -1532,7 +1532,7 @@
         <v>276</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G16" t="n">
         <v>104.6666666666667</v>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
@@ -1603,7 +1603,7 @@
         <v>341</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G17" t="n">
         <v>262</v>
@@ -1627,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="P17" t="n">
         <v>3</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -1745,7 +1745,7 @@
         <v>309</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G19" t="n">
         <v>371</v>
@@ -1769,10 +1769,10 @@
         <v>0.1075804776739356</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="P19" t="n">
         <v>3</v>
@@ -2171,7 +2171,7 @@
         <v>416</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G25" t="n">
         <v>332.3333333333333</v>
@@ -2195,10 +2195,10 @@
         <v>0.1033769063180828</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
@@ -2881,7 +2881,7 @@
         <v>344</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G35" t="n">
         <v>264.3333333333333</v>
@@ -2905,10 +2905,10 @@
         <v>0.1367267283323531</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="O35" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="P35" t="n">
         <v>3</v>
@@ -2952,7 +2952,7 @@
         <v>261</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G36" t="n">
         <v>201</v>
@@ -2976,10 +2976,10 @@
         <v>0.02564102564102564</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="P36" t="n">
         <v>3</v>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3023,7 +3023,7 @@
         <v>278</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G37" t="n">
         <v>479.6666666666667</v>
@@ -3047,10 +3047,10 @@
         <v>0.1303571428571429</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -3094,7 +3094,7 @@
         <v>168</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G38" t="n">
         <v>287.6666666666667</v>
@@ -3118,10 +3118,10 @@
         <v>0.07228915662650603</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="O38" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="P38" t="n">
         <v>3</v>
@@ -3165,7 +3165,7 @@
         <v>224</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G39" t="n">
         <v>272.3333333333333</v>
@@ -3189,10 +3189,10 @@
         <v>0.1458298191869671</v>
       </c>
       <c r="N39" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="O39" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="P39" t="n">
         <v>3</v>
@@ -3236,7 +3236,7 @@
         <v>264</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G40" t="n">
         <v>282</v>
@@ -3260,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="O40" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="P40" t="n">
         <v>3</v>
@@ -3307,7 +3307,7 @@
         <v>226</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G41" t="n">
         <v>334</v>
@@ -3331,10 +3331,10 @@
         <v>0.08741626794258374</v>
       </c>
       <c r="N41" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="O41" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="P41" t="n">
         <v>3</v>
@@ -3378,7 +3378,7 @@
         <v>429</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G42" t="n">
         <v>23</v>
@@ -3402,10 +3402,10 @@
         <v>0.07197786360754022</v>
       </c>
       <c r="N42" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="P42" t="n">
         <v>3</v>
@@ -3449,7 +3449,7 @@
         <v>483</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G43" t="n">
         <v>571.3333333333334</v>
@@ -3473,10 +3473,10 @@
         <v>0.1045881940766245</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="O43" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -3520,7 +3520,7 @@
         <v>410</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G44" t="n">
         <v>288.3333333333333</v>
@@ -3544,10 +3544,10 @@
         <v>0.0682096711781313</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="P44" t="n">
         <v>3</v>
@@ -3591,7 +3591,7 @@
         <v>340</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G45" t="n">
         <v>389.3333333333333</v>
@@ -3615,10 +3615,10 @@
         <v>0.03680981595092025</v>
       </c>
       <c r="N45" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="O45" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="P45" t="n">
         <v>3</v>
@@ -3662,7 +3662,7 @@
         <v>459</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G46" t="n">
         <v>356.3333333333333</v>
@@ -3686,10 +3686,10 @@
         <v>0.04618335628565808</v>
       </c>
       <c r="N46" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="O46" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="P46" t="n">
         <v>3</v>
@@ -3733,7 +3733,7 @@
         <v>38</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G47" t="n">
         <v>7</v>
@@ -3757,10 +3757,10 @@
         <v>0.9546198482368695</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="O47" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="P47" t="n">
         <v>3</v>
@@ -3875,7 +3875,7 @@
         <v>369</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G49" t="n">
         <v>297.6666666666667</v>
@@ -3899,10 +3899,10 @@
         <v>0.09095377820084233</v>
       </c>
       <c r="N49" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="P49" t="n">
         <v>3</v>
@@ -3946,7 +3946,7 @@
         <v>418</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G50" t="n">
         <v>28</v>
@@ -3970,10 +3970,10 @@
         <v>0.09084146817649355</v>
       </c>
       <c r="N50" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="P50" t="n">
         <v>3</v>
@@ -4017,7 +4017,7 @@
         <v>12</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G51" t="n">
         <v>15</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="P51" t="n">
         <v>3</v>
@@ -4088,7 +4088,7 @@
         <v>323</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G52" t="n">
         <v>110.6666666666667</v>
@@ -4112,10 +4112,10 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="P52" t="n">
         <v>3</v>
@@ -4159,7 +4159,7 @@
         <v>95</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G53" t="n">
         <v>221</v>
@@ -4183,10 +4183,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0.25957885891113</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="O53" t="n">
-        <v>0.25957885891113</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="P53" t="n">
         <v>3</v>
@@ -4230,7 +4230,7 @@
         <v>47</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G54" t="n">
         <v>91</v>
@@ -4254,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="O54" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="P54" t="n">
         <v>3</v>
@@ -5011,7 +5011,7 @@
         <v>309</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G65" t="n">
         <v>570.3333333333334</v>
@@ -5035,10 +5035,10 @@
         <v>0.1930397432721377</v>
       </c>
       <c r="N65" t="n">
-        <v>0.462749110224935</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="O65" t="n">
-        <v>0.462749110224935</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="P65" t="n">
         <v>3</v>
@@ -5082,7 +5082,7 @@
         <v>163</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G66" t="n">
         <v>132.6666666666667</v>
@@ -5106,10 +5106,10 @@
         <v>0.1158841158841159</v>
       </c>
       <c r="N66" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="P66" t="n">
         <v>3</v>
@@ -5153,7 +5153,7 @@
         <v>189</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5177,10 +5177,10 @@
         <v>0.1020408163265306</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="P67" t="n">
         <v>3</v>
@@ -5224,7 +5224,7 @@
         <v>15</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -5248,10 +5248,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="P68" t="n">
         <v>3</v>
@@ -5437,7 +5437,7 @@
         <v>468</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G71" t="n">
         <v>224</v>
@@ -5461,10 +5461,10 @@
         <v>0.1203453940470656</v>
       </c>
       <c r="N71" t="n">
-        <v>0.305396186848636</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="O71" t="n">
-        <v>0.305396186848636</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="P71" t="n">
         <v>3</v>
@@ -5508,7 +5508,7 @@
         <v>162</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G72" t="n">
         <v>526</v>
@@ -5532,10 +5532,10 @@
         <v>0.195774670093178</v>
       </c>
       <c r="N72" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="O72" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="P72" t="n">
         <v>3</v>
@@ -6147,7 +6147,7 @@
         <v>233</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G81" t="n">
         <v>262.3333333333333</v>
@@ -6171,10 +6171,10 @@
         <v>0.1120375195414278</v>
       </c>
       <c r="N81" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="P81" t="n">
         <v>3</v>
@@ -6218,7 +6218,7 @@
         <v>133</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G82" t="n">
         <v>138.6666666666667</v>
@@ -6242,10 +6242,10 @@
         <v>0.04379562043795621</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="O82" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -6289,7 +6289,7 @@
         <v>274</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G83" t="n">
         <v>209</v>
@@ -6313,10 +6313,10 @@
         <v>0.1838490566037736</v>
       </c>
       <c r="N83" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="O83" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="P83" t="n">
         <v>3</v>
@@ -6360,7 +6360,7 @@
         <v>364</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G84" t="n">
         <v>34</v>
@@ -6384,10 +6384,10 @@
         <v>0.139295825342337</v>
       </c>
       <c r="N84" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="O84" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="P84" t="n">
         <v>3</v>
@@ -6431,7 +6431,7 @@
         <v>110</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G85" t="n">
         <v>209.3333333333333</v>
@@ -6455,10 +6455,10 @@
         <v>0.06185567010309279</v>
       </c>
       <c r="N85" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="O85" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="P85" t="n">
         <v>3</v>
@@ -6502,7 +6502,7 @@
         <v>193</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G86" t="n">
         <v>171</v>
@@ -6526,10 +6526,10 @@
         <v>0.1263094278807413</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="O86" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="P86" t="n">
         <v>3</v>
@@ -6644,7 +6644,7 @@
         <v>397</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G88" t="n">
         <v>187.6666666666666</v>
@@ -6668,10 +6668,10 @@
         <v>0.07802711107010211</v>
       </c>
       <c r="N88" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="O88" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="P88" t="n">
         <v>3</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -6715,7 +6715,7 @@
         <v>477</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G89" t="n">
         <v>406.3333333333333</v>
@@ -6739,10 +6739,10 @@
         <v>0.07477909683725838</v>
       </c>
       <c r="N89" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="O89" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="P89" t="n">
         <v>3</v>
@@ -7141,7 +7141,7 @@
         <v>481</v>
       </c>
       <c r="F95" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G95" t="n">
         <v>248.3333333333333</v>
@@ -7165,10 +7165,10 @@
         <v>0.1225239661720482</v>
       </c>
       <c r="N95" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="O95" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="P95" t="n">
         <v>3</v>
@@ -7212,7 +7212,7 @@
         <v>498</v>
       </c>
       <c r="F96" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G96" t="n">
         <v>201.3333333333333</v>
@@ -7236,10 +7236,10 @@
         <v>0.1329017851542409</v>
       </c>
       <c r="N96" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="O96" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="P96" t="n">
         <v>3</v>
@@ -8064,7 +8064,7 @@
         <v>457</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G108" t="n">
         <v>367.3333333333333</v>
@@ -8088,10 +8088,10 @@
         <v>0.07121719408143429</v>
       </c>
       <c r="N108" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="O108" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="P108" t="n">
         <v>3</v>
@@ -8135,7 +8135,7 @@
         <v>482</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G109" t="n">
         <v>9.666666666666666</v>
@@ -8159,10 +8159,10 @@
         <v>0.03989642247994184</v>
       </c>
       <c r="N109" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="O109" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="P109" t="n">
         <v>3</v>
@@ -8348,7 +8348,7 @@
         <v>429</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G112" t="n">
         <v>300.6666666666667</v>
@@ -8372,10 +8372,10 @@
         <v>0.1096520286408708</v>
       </c>
       <c r="N112" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="O112" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="P112" t="n">
         <v>3</v>
@@ -8490,7 +8490,7 @@
         <v>441</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G114" t="n">
         <v>299</v>
@@ -8514,10 +8514,10 @@
         <v>0.09115131768568528</v>
       </c>
       <c r="N114" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="O114" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="P114" t="n">
         <v>3</v>
@@ -8561,7 +8561,7 @@
         <v>301</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G115" t="n">
         <v>322.6666666666667</v>
@@ -8585,10 +8585,10 @@
         <v>0.0823202833349287</v>
       </c>
       <c r="N115" t="n">
-        <v>0.341111141986838</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="O115" t="n">
-        <v>0.341111141986838</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="P115" t="n">
         <v>3</v>
@@ -8632,7 +8632,7 @@
         <v>489</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G116" t="n">
         <v>906.3333333333334</v>
@@ -8656,10 +8656,10 @@
         <v>0.05377528981354961</v>
       </c>
       <c r="N116" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="O116" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="P116" t="n">
         <v>3</v>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>수요 상위</t>
+          <t>수요 중위</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
         <v>441</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G123" t="n">
         <v>402</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="O123" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="P123" t="n">
         <v>3</v>
@@ -9271,7 +9271,7 @@
         <v>471</v>
       </c>
       <c r="F125" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G125" t="n">
         <v>339.3333333333333</v>
@@ -9295,10 +9295,10 @@
         <v>0.0411237298266587</v>
       </c>
       <c r="N125" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="O125" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="P125" t="n">
         <v>3</v>
@@ -9768,7 +9768,7 @@
         <v>95</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G132" t="n">
         <v>238.6666666666666</v>
@@ -9792,10 +9792,10 @@
         <v>0.1330882352941176</v>
       </c>
       <c r="N132" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="O132" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="P132" t="n">
         <v>3</v>
@@ -9839,7 +9839,7 @@
         <v>43</v>
       </c>
       <c r="F133" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G133" t="n">
         <v>55.33333333333334</v>
@@ -9863,10 +9863,10 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="O133" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="P133" t="n">
         <v>3</v>
@@ -9910,7 +9910,7 @@
         <v>193</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G134" t="n">
         <v>303</v>
@@ -9934,10 +9934,10 @@
         <v>0.1246313559557017</v>
       </c>
       <c r="N134" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="O134" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="P134" t="n">
         <v>3</v>
@@ -9981,7 +9981,7 @@
         <v>75</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G135" t="n">
         <v>102</v>
@@ -10005,10 +10005,10 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="O135" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="P135" t="n">
         <v>3</v>
@@ -10052,7 +10052,7 @@
         <v>155</v>
       </c>
       <c r="F136" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G136" t="n">
         <v>166.3333333333333</v>
@@ -10076,10 +10076,10 @@
         <v>0.04379562043795621</v>
       </c>
       <c r="N136" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="O136" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="P136" t="n">
         <v>3</v>
@@ -10123,7 +10123,7 @@
         <v>415</v>
       </c>
       <c r="F137" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G137" t="n">
         <v>368.3333333333333</v>
@@ -10147,10 +10147,10 @@
         <v>0.1446991957387437</v>
       </c>
       <c r="N137" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="O137" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="P137" t="n">
         <v>3</v>
@@ -10194,7 +10194,7 @@
         <v>151</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G138" t="n">
         <v>315.6666666666667</v>
@@ -10218,10 +10218,10 @@
         <v>0.03973509933774835</v>
       </c>
       <c r="N138" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="O138" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="P138" t="n">
         <v>3</v>
@@ -10265,7 +10265,7 @@
         <v>375</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G139" t="n">
         <v>228</v>
@@ -10289,10 +10289,10 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="O139" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="P139" t="n">
         <v>3</v>
@@ -10336,7 +10336,7 @@
         <v>353</v>
       </c>
       <c r="F140" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G140" t="n">
         <v>388</v>
@@ -10360,10 +10360,10 @@
         <v>0.05882352941176471</v>
       </c>
       <c r="N140" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="O140" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="P140" t="n">
         <v>3</v>
@@ -10407,7 +10407,7 @@
         <v>5</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -10431,10 +10431,10 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="O141" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="P141" t="n">
         <v>3</v>
@@ -10478,7 +10478,7 @@
         <v>319</v>
       </c>
       <c r="F142" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="G142" t="n">
         <v>209.6666666666666</v>
@@ -10502,10 +10502,10 @@
         <v>0.1129521918002553</v>
       </c>
       <c r="N142" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="O142" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="P142" t="n">
         <v>3</v>
@@ -10549,7 +10549,7 @@
         <v>109</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G143" t="n">
         <v>232</v>
@@ -10573,10 +10573,10 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="O143" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="P143" t="n">
         <v>3</v>
@@ -10620,7 +10620,7 @@
         <v>71</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G144" t="n">
         <v>93.33333333333331</v>
@@ -10644,10 +10644,10 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="O144" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="P144" t="n">
         <v>3</v>
@@ -10691,7 +10691,7 @@
         <v>98</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G145" t="n">
         <v>81.33333333333333</v>
@@ -10715,10 +10715,10 @@
         <v>0.1818181818181819</v>
       </c>
       <c r="N145" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="O145" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="P145" t="n">
         <v>3</v>
@@ -10762,7 +10762,7 @@
         <v>201</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G146" t="n">
         <v>303.6666666666667</v>
@@ -10786,10 +10786,10 @@
         <v>0.06</v>
       </c>
       <c r="N146" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="O146" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="P146" t="n">
         <v>3</v>
@@ -10833,7 +10833,7 @@
         <v>174</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="G147" t="n">
         <v>312.6666666666667</v>
@@ -10857,10 +10857,10 @@
         <v>0.03428571428571429</v>
       </c>
       <c r="N147" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="O147" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="P147" t="n">
         <v>3</v>
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F9" t="n">
         <v>0.2051374145411299</v>
@@ -11362,10 +11362,10 @@
         <v>0.03243243243243243</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F10" t="n">
         <v>0.2004335900090441</v>
@@ -11415,10 +11415,10 @@
         <v>0.02553191489361702</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F11" t="n">
         <v>0.3981295677618628</v>
@@ -11468,10 +11468,10 @@
         <v>0.07037764675526569</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F12" t="n">
         <v>0.4817851398830783</v>
@@ -11521,10 +11521,10 @@
         <v>0.2339320004518243</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="J12" t="n">
         <v>3</v>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 상위</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F13" t="n">
         <v>0.0011011854958523</v>
@@ -11574,10 +11574,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F14" t="n">
         <v>0.1478611366284428</v>
@@ -11627,10 +11627,10 @@
         <v>0.07086614173228346</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F15" t="n">
         <v>0.261803616952978</v>
@@ -11680,10 +11680,10 @@
         <v>0.04477611940298508</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F16" t="n">
         <v>0.1154682386344549</v>
@@ -11733,10 +11733,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="J16" t="n">
         <v>3</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F17" t="n">
         <v>0.2611738807004353</v>
@@ -11786,10 +11786,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F19" t="n">
         <v>0.3871806223139501</v>
@@ -11892,10 +11892,10 @@
         <v>0.1075804776739356</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="J19" t="n">
         <v>3</v>
@@ -12201,7 +12201,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F25" t="n">
         <v>0.3042280023489025</v>
@@ -12210,10 +12210,10 @@
         <v>0.1033769063180828</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="J25" t="n">
         <v>3</v>
@@ -12731,7 +12731,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F35" t="n">
         <v>0.2624588353774778</v>
@@ -12740,10 +12740,10 @@
         <v>0.1367267283323531</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F36" t="n">
         <v>0.2281883551218987</v>
@@ -12793,10 +12793,10 @@
         <v>0.02564102564102564</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="J36" t="n">
         <v>3</v>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -12837,7 +12837,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F37" t="n">
         <v>0.5272427649597402</v>
@@ -12846,10 +12846,10 @@
         <v>0.1303571428571429</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F38" t="n">
         <v>0.4205334769382167</v>
@@ -12899,10 +12899,10 @@
         <v>0.07228915662650603</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="J38" t="n">
         <v>3</v>
@@ -12943,7 +12943,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F39" t="n">
         <v>0.3357113788902203</v>
@@ -12952,10 +12952,10 @@
         <v>0.1458298191869671</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="J39" t="n">
         <v>3</v>
@@ -12996,7 +12996,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F40" t="n">
         <v>0.3182541452104335</v>
@@ -13005,10 +13005,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="J40" t="n">
         <v>3</v>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F41" t="n">
         <v>0.4096972760817491</v>
@@ -13058,10 +13058,10 @@
         <v>0.08741626794258374</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F42" t="n">
         <v>0.020796896772864</v>
@@ -13111,10 +13111,10 @@
         <v>0.07197786360754022</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F43" t="n">
         <v>0.4936783384019001</v>
@@ -13164,10 +13164,10 @@
         <v>0.1045881940766245</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="J43" t="n">
         <v>3</v>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F44" t="n">
         <v>0.2655110230628451</v>
@@ -13217,10 +13217,10 @@
         <v>0.0682096711781313</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F45" t="n">
         <v>0.3886228313634106</v>
@@ -13270,10 +13270,10 @@
         <v>0.03680981595092025</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F46" t="n">
         <v>0.3138411838772603</v>
@@ -13323,10 +13323,10 @@
         <v>0.04618335628565808</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F47" t="n">
         <v>0.032183814105257</v>
@@ -13376,10 +13376,10 @@
         <v>0.9546198482368695</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -13473,7 +13473,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F49" t="n">
         <v>0.2865279309795805</v>
@@ -13482,10 +13482,10 @@
         <v>0.09095377820084233</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -13526,7 +13526,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F50" t="n">
         <v>0.0255824556496562</v>
@@ -13535,10 +13535,10 @@
         <v>0.09084146817649355</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F51" t="n">
         <v>0.2006693383532846</v>
@@ -13588,10 +13588,10 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="J51" t="n">
         <v>3</v>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F52" t="n">
         <v>0.1131027623352295</v>
@@ -13641,10 +13641,10 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -13685,7 +13685,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F53" t="n">
         <v>0.4787365767333901</v>
@@ -13694,10 +13694,10 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25957885891113</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="I53" t="n">
-        <v>0.25957885891113</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -13738,7 +13738,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F54" t="n">
         <v>0.3477738096487907</v>
@@ -13747,10 +13747,10 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
@@ -14321,7 +14321,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F65" t="n">
         <v>0.5952075874026673</v>
@@ -14330,10 +14330,10 @@
         <v>0.1930397432721377</v>
       </c>
       <c r="H65" t="n">
-        <v>0.462749110224935</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="I65" t="n">
-        <v>0.462749110224935</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
@@ -14374,7 +14374,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F66" t="n">
         <v>0.1976726557730393</v>
@@ -14383,10 +14383,10 @@
         <v>0.1158841158841159</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
@@ -14427,7 +14427,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -14436,10 +14436,10 @@
         <v>0.1020408163265306</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F68" t="n">
         <v>0.0108114159662646</v>
@@ -14489,10 +14489,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="J68" t="n">
         <v>3</v>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F71" t="n">
         <v>0.1958431664988423</v>
@@ -14648,10 +14648,10 @@
         <v>0.1203453940470656</v>
       </c>
       <c r="H71" t="n">
-        <v>0.305396186848636</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="I71" t="n">
-        <v>0.305396186848636</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="J71" t="n">
         <v>3</v>
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F72" t="n">
         <v>0.78680479825518</v>
@@ -14701,10 +14701,10 @@
         <v>0.195774670093178</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="J72" t="n">
         <v>3</v>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F81" t="n">
         <v>0.3164180297242954</v>
@@ -15178,10 +15178,10 @@
         <v>0.1120375195414278</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -15222,7 +15222,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F82" t="n">
         <v>0.2361623444441073</v>
@@ -15231,10 +15231,10 @@
         <v>0.04379562043795621</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="J82" t="n">
         <v>3</v>
@@ -15275,7 +15275,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F83" t="n">
         <v>0.2314199132474892</v>
@@ -15284,10 +15284,10 @@
         <v>0.1838490566037736</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="J83" t="n">
         <v>3</v>
@@ -15328,7 +15328,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F84" t="n">
         <v>0.0329226182635174</v>
@@ -15337,10 +15337,10 @@
         <v>0.139295825342337</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="J84" t="n">
         <v>3</v>
@@ -15381,7 +15381,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F85" t="n">
         <v>0.4071925075669307</v>
@@ -15390,10 +15390,10 @@
         <v>0.06185567010309279</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="J85" t="n">
         <v>3</v>
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F86" t="n">
         <v>0.2296776803799888</v>
@@ -15443,10 +15443,10 @@
         <v>0.1263094278807413</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="J86" t="n">
         <v>3</v>
@@ -15540,7 +15540,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F88" t="n">
         <v>0.1751204810202206</v>
@@ -15549,10 +15549,10 @@
         <v>0.07802711107010211</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="J88" t="n">
         <v>3</v>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -15593,7 +15593,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F89" t="n">
         <v>0.3527345051160103</v>
@@ -15602,10 +15602,10 @@
         <v>0.07477909683725838</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="J89" t="n">
         <v>3</v>
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F95" t="n">
         <v>0.2149093505434027</v>
@@ -15920,10 +15920,10 @@
         <v>0.1225239661720482</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="J95" t="n">
         <v>3</v>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F96" t="n">
         <v>0.1720348935371041</v>
@@ -15973,10 +15973,10 @@
         <v>0.1329017851542409</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="J96" t="n">
         <v>3</v>
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F108" t="n">
         <v>0.3240687900487338</v>
@@ -16609,10 +16609,10 @@
         <v>0.07121719408143429</v>
       </c>
       <c r="H108" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="I108" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="J108" t="n">
         <v>3</v>
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F109" t="n">
         <v>0.0083591781576696</v>
@@ -16662,10 +16662,10 @@
         <v>0.03989642247994184</v>
       </c>
       <c r="H109" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="J109" t="n">
         <v>3</v>
@@ -16812,7 +16812,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F112" t="n">
         <v>0.2718666795525124</v>
@@ -16821,10 +16821,10 @@
         <v>0.1096520286408708</v>
       </c>
       <c r="H112" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="J112" t="n">
         <v>3</v>
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F114" t="n">
         <v>0.2674391673483604</v>
@@ -16927,10 +16927,10 @@
         <v>0.09115131768568528</v>
       </c>
       <c r="H114" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="J114" t="n">
         <v>3</v>
@@ -16971,7 +16971,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F115" t="n">
         <v>0.3410131426255853</v>
@@ -16980,10 +16980,10 @@
         <v>0.0823202833349287</v>
       </c>
       <c r="H115" t="n">
-        <v>0.341111141986838</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="I115" t="n">
-        <v>0.341111141986838</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="J115" t="n">
         <v>3</v>
@@ -17024,7 +17024,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F116" t="n">
         <v>0.7795999680122426</v>
@@ -17033,10 +17033,10 @@
         <v>0.05377528981354961</v>
       </c>
       <c r="H116" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="J116" t="n">
         <v>3</v>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>수요 상위</t>
+          <t>수요 중위</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F123" t="n">
         <v>0.3595670410503039</v>
@@ -17404,10 +17404,10 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="J123" t="n">
         <v>3</v>
@@ -17501,7 +17501,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F125" t="n">
         <v>0.295967901342231</v>
@@ -17510,10 +17510,10 @@
         <v>0.0411237298266587</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="J125" t="n">
         <v>3</v>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F132" t="n">
         <v>0.5170066198206746</v>
@@ -17881,10 +17881,10 @@
         <v>0.1330882352941176</v>
       </c>
       <c r="H132" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="J132" t="n">
         <v>3</v>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F133" t="n">
         <v>0.2283316038840079</v>
@@ -17934,10 +17934,10 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="J133" t="n">
         <v>3</v>
@@ -17978,7 +17978,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F134" t="n">
         <v>0.4069727319013836</v>
@@ -17987,10 +17987,10 @@
         <v>0.1246313559557017</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="J134" t="n">
         <v>3</v>
@@ -18031,7 +18031,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F135" t="n">
         <v>0.265045797380282</v>
@@ -18040,10 +18040,10 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="J135" t="n">
         <v>3</v>
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F136" t="n">
         <v>0.2559463474428509</v>
@@ -18093,10 +18093,10 @@
         <v>0.04379562043795621</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="J136" t="n">
         <v>3</v>
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F137" t="n">
         <v>0.3375120411071955</v>
@@ -18146,10 +18146,10 @@
         <v>0.1446991957387437</v>
       </c>
       <c r="H137" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="J137" t="n">
         <v>3</v>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F138" t="n">
         <v>0.4940415218194545</v>
@@ -18199,10 +18199,10 @@
         <v>0.03973509933774835</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="J138" t="n">
         <v>3</v>
@@ -18243,7 +18243,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F139" t="n">
         <v>0.2179458060877966</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="J139" t="n">
         <v>3</v>
@@ -18296,7 +18296,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F140" t="n">
         <v>0.3808201961902997</v>
@@ -18305,10 +18305,10 @@
         <v>0.05882352941176471</v>
       </c>
       <c r="H140" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="J140" t="n">
         <v>3</v>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -18358,10 +18358,10 @@
         <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="J141" t="n">
         <v>3</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="F142" t="n">
         <v>0.215535457316114</v>
@@ -18411,10 +18411,10 @@
         <v>0.1129521918002553</v>
       </c>
       <c r="H142" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="J142" t="n">
         <v>3</v>
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F143" t="n">
         <v>0.454263085399187</v>
@@ -18464,10 +18464,10 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="J143" t="n">
         <v>3</v>
@@ -18508,7 +18508,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F144" t="n">
         <v>0.2533219031874272</v>
@@ -18517,10 +18517,10 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="J144" t="n">
         <v>3</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F145" t="n">
         <v>0.1721507225361336</v>
@@ -18570,10 +18570,10 @@
         <v>0.1818181818181819</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="J145" t="n">
         <v>3</v>
@@ -18614,7 +18614,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F146" t="n">
         <v>0.3982246984762633</v>
@@ -18623,10 +18623,10 @@
         <v>0.06</v>
       </c>
       <c r="H146" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="J146" t="n">
         <v>3</v>
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="F147" t="n">
         <v>0.4471977650045322</v>
@@ -18676,10 +18676,10 @@
         <v>0.03428571428571429</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="J147" t="n">
         <v>3</v>
